--- a/Utilization Report/archive/Utilization_Report_July_2026_H1.xlsx
+++ b/Utilization Report/archive/Utilization_Report_July_2026_H1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="57">
   <si>
     <t>Employee</t>
   </si>
@@ -139,16 +139,10 @@
     <t>July 2026 H1  (2026-07-01 to 2026-07-14 inclusive)</t>
   </si>
   <si>
-    <t>Run date (UTC)</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
     <t>Generated (UTC)</t>
   </si>
   <si>
-    <t>2026-07-16 07:14:38</t>
+    <t>2026-07-16 10:03:03</t>
   </si>
   <si>
     <t>Source</t>
@@ -565,7 +559,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="24.2109375" customWidth="true" bestFit="true"/>
@@ -652,14 +646,6 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="s" s="1">
-        <v>57</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>58</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Utilization Report/archive/Utilization_Report_July_2026_H1.xlsx
+++ b/Utilization Report/archive/Utilization_Report_July_2026_H1.xlsx
@@ -142,7 +142,7 @@
     <t>Generated (UTC)</t>
   </si>
   <si>
-    <t>2026-07-16 10:03:03</t>
+    <t>2026-07-16 15:22:35</t>
   </si>
   <si>
     <t>Source</t>
